--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_65274_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_65274_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbc261479cc8544e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5901a4162bdb4701"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,96 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6179</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6373</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5591</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5604</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
